--- a/Result/profitability/1414.xlsx
+++ b/Result/profitability/1414.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04125</v>
+        <v>0.06875000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>11.40375</v>
+        <v>11.4825</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01625</v>
+        <v>0.05625</v>
       </c>
       <c r="N3" t="n">
-        <v>10.2125</v>
+        <v>10.14375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.02125</v>
+        <v>0.02125</v>
       </c>
       <c r="N4" t="n">
-        <v>8.37125</v>
+        <v>8.25375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.63</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0975</v>
+        <v>-0.0625</v>
       </c>
       <c r="N5" t="n">
-        <v>5.281249999999999</v>
+        <v>5.2325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.15375</v>
+        <v>-0.12625</v>
       </c>
       <c r="N6" t="n">
-        <v>3.02125</v>
+        <v>3.255</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.20375</v>
+        <v>-0.1725</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>0.85875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.25875</v>
+        <v>-0.22625</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.315</v>
+        <v>-1.155</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.06875000000000001</v>
+        <v>-0.06874999999999998</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
@@ -9812,6 +9812,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>127</v>
+      </c>
+      <c r="D75" t="n">
+        <v>112</v>
+      </c>
+      <c r="E75" t="n">
+        <v>16</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.98%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>69</v>
+      </c>
+      <c r="J75" t="n">
+        <v>61</v>
+      </c>
+      <c r="K75" t="n">
+        <v>63</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.08374999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.56375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.280000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1153153153153155</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.3899999999999988</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03054032889584957</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
